--- a/data/b2_bonsucesso/B2 Bonsucesso 02-2026.xlsx
+++ b/data/b2_bonsucesso/B2 Bonsucesso 02-2026.xlsx
@@ -4366,133 +4366,133 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>439.55</v>
+        <v>411.17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>4006.75</v>
+        <v>65109.08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46058</v>
+        <v>46061</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>64480.75</v>
+        <v>3863.92</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>1002.23</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46061</v>
+        <v>46064</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3592.37</v>
+        <v>1678.29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46061</v>
+        <v>46065</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>4136.43</v>
+        <v>1387.78</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46063</v>
+        <v>46068</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>3600</v>
+        <v>11109.76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46065</v>
+        <v>46068</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1427.69</v>
+        <v>1782.43</v>
       </c>
     </row>
     <row r="10">
@@ -4501,57 +4501,57 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>10548.61</v>
+        <v>3730.49</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46068</v>
+        <v>46071</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>2117.91</v>
+        <v>2469.88</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46068</v>
+        <v>46073</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>3757.68</v>
+        <v>23006.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46071</v>
+        <v>46075</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -4564,61 +4564,61 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>857.33</v>
+        <v>1634.66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46073</v>
+        <v>46075</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>22678.11</v>
+        <v>3867.16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46075</v>
+        <v>46077</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Manutenção preventiva das bombas</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>1982.9</v>
+        <v>3742.11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46075</v>
+        <v>46079</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3831.01</v>
+        <v>1437.58</v>
       </c>
     </row>
     <row r="17">
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3610.66</v>
+        <v>3450.95</v>
       </c>
     </row>
   </sheetData>
